--- a/Versão5/ILUM/Ontologia_Iluminação.xlsx
+++ b/Versão5/ILUM/Ontologia_Iluminação.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9A9AD9-E4AF-472C-BB4B-3C057E892541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE370D6-D5CB-4D35-A6C9-9C840A7A7265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -632,15 +632,9 @@
     <t>CTI_Projeto_01</t>
   </si>
   <si>
-    <t>fabricante</t>
-  </si>
-  <si>
     <t>"Lumicenter Lighting"</t>
   </si>
   <si>
-    <t>fornecedor</t>
-  </si>
-  <si>
     <t>"Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
@@ -942,6 +936,12 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>quem.fabricou</t>
+  </si>
+  <si>
+    <t>quem.forneceu</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1489,20 +1489,11 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -1569,33 +1560,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1645,11 +1614,33 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2214,7 +2205,7 @@
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" s="45" t="s">
         <v>96</v>
@@ -2382,7 +2373,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46139.498362615741</v>
+        <v>46213.786009374999</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>96</v>
@@ -2426,7 +2417,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>96</v>
@@ -2437,7 +2428,7 @@
         <v>75</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C23" s="45" t="s">
         <v>97</v>
@@ -2484,7 +2475,7 @@
     <col min="20" max="20" width="6.15234375" customWidth="1"/>
     <col min="21" max="21" width="10.15234375" customWidth="1"/>
     <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.4609375" style="70" customWidth="1"/>
+    <col min="23" max="23" width="6.4609375" customWidth="1"/>
     <col min="24" max="24" width="10.84375" customWidth="1"/>
     <col min="25" max="25" width="16.84375" style="56" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5.61328125" style="37" customWidth="1"/>
@@ -2579,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>86</v>
@@ -2588,10 +2579,10 @@
         <v>87</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F2" s="65" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G2" s="38" t="s">
         <v>9</v>
@@ -2625,7 +2616,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>88</v>
@@ -2646,7 +2637,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W2" s="69" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-ILU-",A2)</f>
@@ -2671,7 +2662,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>86</v>
@@ -2680,10 +2671,10 @@
         <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F3" s="65" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G3" s="38" t="s">
         <v>9</v>
@@ -2717,7 +2708,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>88</v>
@@ -2738,7 +2729,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W3" s="69" t="str">
         <f t="shared" si="3"/>
@@ -2763,7 +2754,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C4" s="65" t="s">
         <v>86</v>
@@ -2772,10 +2763,10 @@
         <v>87</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>9</v>
@@ -2809,7 +2800,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>88</v>
@@ -2830,7 +2821,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W4" s="69" t="str">
         <f t="shared" si="3"/>
@@ -2855,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C5" s="65" t="s">
         <v>86</v>
@@ -2864,10 +2855,10 @@
         <v>87</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>9</v>
@@ -2901,7 +2892,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>88</v>
@@ -2922,7 +2913,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W5" s="69" t="str">
         <f t="shared" si="3"/>
@@ -2947,7 +2938,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C6" s="65" t="s">
         <v>86</v>
@@ -2956,10 +2947,10 @@
         <v>87</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>9</v>
@@ -2993,7 +2984,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>88</v>
@@ -3014,7 +3005,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W6" s="69" t="str">
         <f t="shared" si="3"/>
@@ -3042,16 +3033,16 @@
         <v>46</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G7" s="38" t="s">
         <v>9</v>
@@ -3085,16 +3076,16 @@
         <v>Circuito.Luz.Geral</v>
       </c>
       <c r="P7" s="62" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q7" s="62" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="36" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="T7" s="36" t="str">
         <f t="shared" ref="T7:T8" si="9">SUBSTITUTE(D7, "_", " ")</f>
@@ -3105,20 +3096,20 @@
         <v>Sistemas.de.Iluminação</v>
       </c>
       <c r="V7" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W7" s="69" t="str">
         <f t="shared" ref="W7:W35" si="11">CONCATENATE("Key-ILU-",A7)</f>
         <v>Key-ILU-7</v>
       </c>
       <c r="X7" s="67" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y7" s="67" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Z7" s="35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AA7" s="30" t="str">
         <f t="shared" ref="AA7:AA8" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
@@ -3133,16 +3124,16 @@
         <v>46</v>
       </c>
       <c r="C8" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="48" t="s">
         <v>270</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>272</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>9</v>
@@ -3176,16 +3167,16 @@
         <v>Circuito.Luz.Emergência</v>
       </c>
       <c r="P8" s="62" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q8" s="62" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="36" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="T8" s="36" t="str">
         <f t="shared" si="9"/>
@@ -3196,20 +3187,20 @@
         <v>Sistemas.de.Iluminação</v>
       </c>
       <c r="V8" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W8" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-8</v>
       </c>
       <c r="X8" s="67" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y8" s="67" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Z8" s="35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f t="shared" si="12"/>
@@ -3224,10 +3215,10 @@
         <v>46</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E9" s="48" t="s">
         <v>45</v>
@@ -3279,26 +3270,26 @@
         <v>44</v>
       </c>
       <c r="T9" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U9" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V9" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W9" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-9</v>
       </c>
       <c r="X9" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y9" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z9" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA9" s="30" t="s">
         <v>165</v>
@@ -3312,10 +3303,10 @@
         <v>46</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E10" s="48" t="s">
         <v>45</v>
@@ -3367,26 +3358,26 @@
         <v>44</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U10" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V10" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W10" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-10</v>
       </c>
       <c r="X10" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y10" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z10" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA10" s="30" t="s">
         <v>166</v>
@@ -3400,10 +3391,10 @@
         <v>46</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E11" s="48" t="s">
         <v>45</v>
@@ -3455,26 +3446,26 @@
         <v>44</v>
       </c>
       <c r="T11" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U11" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V11" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W11" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-11</v>
       </c>
       <c r="X11" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z11" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA11" s="30" t="s">
         <v>167</v>
@@ -3488,10 +3479,10 @@
         <v>46</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E12" s="48" t="s">
         <v>45</v>
@@ -3543,26 +3534,26 @@
         <v>44</v>
       </c>
       <c r="T12" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U12" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V12" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W12" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-12</v>
       </c>
       <c r="X12" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y12" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z12" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA12" s="30" t="s">
         <v>168</v>
@@ -3576,10 +3567,10 @@
         <v>46</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E13" s="48" t="s">
         <v>45</v>
@@ -3631,26 +3622,26 @@
         <v>44</v>
       </c>
       <c r="T13" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U13" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V13" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W13" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-13</v>
       </c>
       <c r="X13" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y13" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z13" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA13" s="30" t="s">
         <v>169</v>
@@ -3664,10 +3655,10 @@
         <v>46</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E14" s="48" t="s">
         <v>45</v>
@@ -3719,26 +3710,26 @@
         <v>44</v>
       </c>
       <c r="T14" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U14" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V14" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W14" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-14</v>
       </c>
       <c r="X14" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y14" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z14" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA14" s="30" t="s">
         <v>170</v>
@@ -3752,10 +3743,10 @@
         <v>46</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E15" s="48" t="s">
         <v>45</v>
@@ -3807,26 +3798,26 @@
         <v>44</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W15" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-15</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y15" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z15" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA15" s="30" t="s">
         <v>171</v>
@@ -3840,10 +3831,10 @@
         <v>46</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E16" s="48" t="s">
         <v>45</v>
@@ -3883,10 +3874,10 @@
         <v>Luz.Externa</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="R16" s="35" t="s">
         <v>9</v>
@@ -3895,29 +3886,29 @@
         <v>44</v>
       </c>
       <c r="T16" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U16" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V16" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W16" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-16</v>
       </c>
       <c r="X16" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y16" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z16" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3928,16 +3919,16 @@
         <v>46</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="48" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>9</v>
@@ -3971,10 +3962,10 @@
         <v>Luz.Externa.Urbana</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R17" s="35" t="s">
         <v>9</v>
@@ -3983,29 +3974,29 @@
         <v>44</v>
       </c>
       <c r="T17" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U17" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V17" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W17" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-17</v>
       </c>
       <c r="X17" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y17" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z17" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4016,10 +4007,10 @@
         <v>46</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E18" s="48" t="s">
         <v>45</v>
@@ -4071,26 +4062,26 @@
         <v>44</v>
       </c>
       <c r="T18" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U18" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V18" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W18" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-18</v>
       </c>
       <c r="X18" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y18" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z18" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA18" s="30" t="s">
         <v>183</v>
@@ -4104,10 +4095,10 @@
         <v>46</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E19" s="48" t="s">
         <v>45</v>
@@ -4159,26 +4150,26 @@
         <v>44</v>
       </c>
       <c r="T19" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V19" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W19" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-19</v>
       </c>
       <c r="X19" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y19" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z19" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA19" s="30" t="s">
         <v>172</v>
@@ -4192,10 +4183,10 @@
         <v>46</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E20" s="48" t="s">
         <v>45</v>
@@ -4247,26 +4238,26 @@
         <v>44</v>
       </c>
       <c r="T20" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U20" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V20" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W20" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-20</v>
       </c>
       <c r="X20" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y20" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z20" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA20" s="30" t="s">
         <v>173</v>
@@ -4280,10 +4271,10 @@
         <v>46</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E21" s="48" t="s">
         <v>45</v>
@@ -4335,26 +4326,26 @@
         <v>44</v>
       </c>
       <c r="T21" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U21" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V21" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W21" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-21</v>
       </c>
       <c r="X21" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y21" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z21" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA21" s="30" t="s">
         <v>174</v>
@@ -4368,10 +4359,10 @@
         <v>46</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E22" s="48" t="s">
         <v>45</v>
@@ -4423,26 +4414,26 @@
         <v>44</v>
       </c>
       <c r="T22" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U22" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V22" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W22" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-22</v>
       </c>
       <c r="X22" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y22" s="67" t="s">
         <v>164</v>
       </c>
       <c r="Z22" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA22" s="30" t="s">
         <v>175</v>
@@ -4456,10 +4447,10 @@
         <v>46</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>45</v>
@@ -4511,26 +4502,26 @@
         <v>44</v>
       </c>
       <c r="T23" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U23" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V23" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W23" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-23</v>
       </c>
       <c r="X23" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y23" s="67" t="s">
         <v>164</v>
       </c>
       <c r="Z23" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA23" s="30" t="s">
         <v>176</v>
@@ -4544,16 +4535,16 @@
         <v>46</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>45</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G24" s="49" t="s">
         <v>9</v>
@@ -4587,10 +4578,10 @@
         <v>Luz.TuboFluorescente</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R24" s="35" t="s">
         <v>9</v>
@@ -4599,29 +4590,29 @@
         <v>44</v>
       </c>
       <c r="T24" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U24" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V24" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W24" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-24</v>
       </c>
       <c r="X24" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y24" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z24" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4632,10 +4623,10 @@
         <v>46</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E25" s="48" t="s">
         <v>45</v>
@@ -4687,26 +4678,26 @@
         <v>44</v>
       </c>
       <c r="T25" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U25" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V25" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W25" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-25</v>
       </c>
       <c r="X25" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y25" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z25" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA25" s="30" t="s">
         <v>177</v>
@@ -4720,10 +4711,10 @@
         <v>46</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E26" s="48" t="s">
         <v>45</v>
@@ -4775,26 +4766,26 @@
         <v>44</v>
       </c>
       <c r="T26" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U26" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V26" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W26" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-26</v>
       </c>
       <c r="X26" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y26" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z26" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA26" s="30" t="s">
         <v>178</v>
@@ -4808,10 +4799,10 @@
         <v>46</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E27" s="48" t="s">
         <v>45</v>
@@ -4863,26 +4854,26 @@
         <v>44</v>
       </c>
       <c r="T27" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U27" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V27" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W27" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-27</v>
       </c>
       <c r="X27" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y27" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z27" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA27" s="30" t="s">
         <v>184</v>
@@ -4896,10 +4887,10 @@
         <v>46</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E28" s="48" t="s">
         <v>45</v>
@@ -4951,26 +4942,26 @@
         <v>44</v>
       </c>
       <c r="T28" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U28" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V28" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W28" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-28</v>
       </c>
       <c r="X28" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y28" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z28" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA28" s="30" t="s">
         <v>179</v>
@@ -4984,16 +4975,16 @@
         <v>46</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E29" s="48" t="s">
         <v>45</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G29" s="49" t="s">
         <v>9</v>
@@ -5039,26 +5030,26 @@
         <v>44</v>
       </c>
       <c r="T29" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U29" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V29" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W29" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-29</v>
       </c>
       <c r="X29" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y29" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z29" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA29" s="30" t="s">
         <v>180</v>
@@ -5072,10 +5063,10 @@
         <v>46</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E30" s="48" t="s">
         <v>45</v>
@@ -5127,26 +5118,26 @@
         <v>44</v>
       </c>
       <c r="T30" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U30" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V30" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W30" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-30</v>
       </c>
       <c r="X30" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y30" s="67" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z30" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA30" s="30" t="s">
         <v>181</v>
@@ -5160,10 +5151,10 @@
         <v>46</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E31" s="48" t="s">
         <v>45</v>
@@ -5215,26 +5206,26 @@
         <v>44</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W31" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-31</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y31" s="67" t="s">
         <v>163</v>
       </c>
       <c r="Z31" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA31" s="30" t="s">
         <v>182</v>
@@ -5248,16 +5239,16 @@
         <v>46</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F32" s="50" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G32" s="49" t="s">
         <v>9</v>
@@ -5291,10 +5282,10 @@
         <v>Acessório.Luz</v>
       </c>
       <c r="P32" s="30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="Q32" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R32" s="35" t="s">
         <v>9</v>
@@ -5303,29 +5294,29 @@
         <v>44</v>
       </c>
       <c r="T32" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U32" s="36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V32" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W32" s="69" t="str">
         <f t="shared" si="11"/>
         <v>Key-ILU-32</v>
       </c>
       <c r="X32" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y32" s="67" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Z32" s="35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AA32" s="30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5336,16 +5327,16 @@
         <v>46</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E33" s="48" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G33" s="49" t="s">
         <v>9</v>
@@ -5379,10 +5370,10 @@
         <v>Ponto.Iluminado</v>
       </c>
       <c r="P33" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q33" s="30" t="s">
         <v>200</v>
-      </c>
-      <c r="Q33" s="30" t="s">
-        <v>202</v>
       </c>
       <c r="R33" s="35" t="s">
         <v>9</v>
@@ -5391,13 +5382,13 @@
         <v>44</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W33" s="69" t="str">
         <f t="shared" si="11"/>
@@ -5413,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="AA33" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5424,16 +5415,16 @@
         <v>46</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G34" s="49" t="s">
         <v>9</v>
@@ -5467,10 +5458,10 @@
         <v>Linha.Iluminada</v>
       </c>
       <c r="P34" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R34" s="35" t="s">
         <v>9</v>
@@ -5479,13 +5470,13 @@
         <v>44</v>
       </c>
       <c r="T34" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U34" s="36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="V34" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W34" s="69" t="str">
         <f t="shared" si="11"/>
@@ -5501,7 +5492,7 @@
         <v>9</v>
       </c>
       <c r="AA34" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -5512,16 +5503,16 @@
         <v>46</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G35" s="49" t="s">
         <v>9</v>
@@ -5555,10 +5546,10 @@
         <v>Area.Iluminada</v>
       </c>
       <c r="P35" s="30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R35" s="35" t="s">
         <v>9</v>
@@ -5567,13 +5558,13 @@
         <v>44</v>
       </c>
       <c r="T35" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U35" s="36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="V35" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="W35" s="69" t="str">
         <f t="shared" si="11"/>
@@ -5589,7 +5580,7 @@
         <v>9</v>
       </c>
       <c r="AA35" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -5597,60 +5588,58 @@
     <sortCondition ref="F7:F929"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A35">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA9:AA35">
-    <cfRule type="cellIs" dxfId="25" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="43" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1479"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="duplicateValues" dxfId="23" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31 F33:F35">
-    <cfRule type="duplicateValues" dxfId="21" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36:F1048576 F9:F30">
-    <cfRule type="duplicateValues" dxfId="19" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1451"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:X32">
-    <cfRule type="containsText" dxfId="16" priority="37" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="37" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y30">
-    <cfRule type="duplicateValues" dxfId="15" priority="34"/>
-    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="10" priority="34"/>
+    <cfRule type="containsText" dxfId="9" priority="35" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y30)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="13" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A35">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5865,7 +5854,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5890,11 +5879,11 @@
     <col min="5" max="5" width="7.23046875" customWidth="1"/>
     <col min="6" max="6" width="5.3828125" customWidth="1"/>
     <col min="7" max="7" width="59" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.3046875" customWidth="1"/>
+    <col min="8" max="8" width="7.765625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="4.69140625" customWidth="1"/>
     <col min="11" max="11" width="5.53515625" customWidth="1"/>
-    <col min="12" max="12" width="5.3046875" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.4609375" customWidth="1"/>
     <col min="14" max="14" width="6.4609375" customWidth="1"/>
     <col min="15" max="15" width="5.84375" customWidth="1"/>
@@ -5971,7 +5960,7 @@
         <v>185</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D2" s="60" t="s">
         <v>9</v>
@@ -5983,7 +5972,7 @@
         <v>80</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H2" s="59" t="s">
         <v>9</v>
@@ -6027,10 +6016,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D3" s="60" t="s">
         <v>85</v>
@@ -6042,43 +6031,43 @@
         <v>80</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H3" s="59" t="s">
         <v>80</v>
       </c>
       <c r="I3" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="J3" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="R3" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S3" s="25" t="s">
         <v>244</v>
-      </c>
-      <c r="J3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="R3" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6086,10 +6075,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D4" s="60" t="s">
         <v>85</v>
@@ -6101,13 +6090,13 @@
         <v>80</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H4" s="59" t="s">
         <v>80</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J4" s="59" t="s">
         <v>9</v>
@@ -6128,16 +6117,16 @@
         <v>9</v>
       </c>
       <c r="P4" s="59" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R4" s="59" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6145,28 +6134,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H5" s="59" t="s">
         <v>80</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J5" s="59" t="s">
         <v>9</v>
@@ -6187,16 +6176,16 @@
         <v>9</v>
       </c>
       <c r="P5" s="59" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R5" s="59" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6204,28 +6193,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D6" s="60" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H6" s="59" t="s">
         <v>80</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J6" s="59" t="s">
         <v>9</v>
@@ -6246,16 +6235,16 @@
         <v>9</v>
       </c>
       <c r="P6" s="59" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R6" s="59" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6263,7 +6252,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C7" s="63" t="s">
         <v>100</v>
@@ -6272,49 +6261,49 @@
         <v>85</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H7" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J7" s="59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L7" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N7" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P7" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R7" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S7" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R7" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6322,7 +6311,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C8" s="63" t="s">
         <v>100</v>
@@ -6331,49 +6320,49 @@
         <v>85</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H8" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I8" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J8" s="59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L8" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N8" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P8" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R8" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S8" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R8" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6381,7 +6370,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C9" s="63" t="s">
         <v>100</v>
@@ -6390,49 +6379,49 @@
         <v>85</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H9" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I9" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J9" s="59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L9" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N9" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O9" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P9" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R9" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S9" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R9" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6440,7 +6429,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C10" s="63" t="s">
         <v>100</v>
@@ -6449,49 +6438,49 @@
         <v>85</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H10" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I10" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J10" s="59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L10" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N10" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P10" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R10" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S10" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q10" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R10" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6499,7 +6488,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>101</v>
@@ -6508,49 +6497,49 @@
         <v>85</v>
       </c>
       <c r="E11" s="64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H11" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J11" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="K11" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>232</v>
-      </c>
       <c r="L11" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N11" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O11" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P11" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R11" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S11" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q11" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R11" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S11" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6558,7 +6547,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C12" s="63" t="s">
         <v>101</v>
@@ -6567,49 +6556,49 @@
         <v>85</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H12" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I12" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I12" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J12" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>232</v>
-      </c>
       <c r="L12" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N12" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O12" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P12" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R12" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q12" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R12" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S12" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6617,7 +6606,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C13" s="63" t="s">
         <v>101</v>
@@ -6626,49 +6615,49 @@
         <v>85</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H13" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I13" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I13" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J13" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="K13" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="K13" s="25" t="s">
-        <v>232</v>
-      </c>
       <c r="L13" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N13" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O13" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P13" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R13" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S13" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q13" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R13" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S13" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6676,7 +6665,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C14" s="63" t="s">
         <v>101</v>
@@ -6685,49 +6674,49 @@
         <v>85</v>
       </c>
       <c r="E14" s="64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F14" s="23" t="s">
         <v>80</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H14" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I14" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="J14" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="K14" s="25" t="s">
-        <v>232</v>
-      </c>
       <c r="L14" s="59" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N14" s="59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O14" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P14" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q14" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R14" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="S14" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="Q14" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="R14" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="S14" s="25" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -6800,22 +6789,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ILUM/Ontologia_Iluminação.xlsx
+++ b/Versão5/ILUM/Ontologia_Iluminação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE370D6-D5CB-4D35-A6C9-9C840A7A7265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EFF1C4-94F1-45DF-AF15-3029E2BCB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46213.786009374999</v>
+        <v>46214.378321643519</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>96</v>
@@ -5872,25 +5872,25 @@
   <dimension ref="A1:S14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" customWidth="1"/>
-    <col min="4" max="4" width="9.07421875" customWidth="1"/>
-    <col min="5" max="5" width="7.23046875" customWidth="1"/>
-    <col min="6" max="6" width="5.3828125" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="59" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.765625" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" customWidth="1"/>
-    <col min="11" max="11" width="5.53515625" customWidth="1"/>
+    <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4609375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.23046875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.4609375" customWidth="1"/>
-    <col min="14" max="14" width="6.4609375" customWidth="1"/>
-    <col min="15" max="15" width="5.84375" customWidth="1"/>
-    <col min="16" max="16" width="4.69140625" customWidth="1"/>
-    <col min="17" max="17" width="15.4609375" customWidth="1"/>
-    <col min="18" max="18" width="6.765625" customWidth="1"/>
-    <col min="19" max="19" width="15.3828125" customWidth="1"/>
+    <col min="13" max="13" width="17.15234375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.07421875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">

--- a/Versão5/ILUM/Ontologia_Iluminação.xlsx
+++ b/Versão5/ILUM/Ontologia_Iluminação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EFF1C4-94F1-45DF-AF15-3029E2BCB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9386F8-C92F-4BEA-AE5C-AF498A1F64A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="289">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -209,9 +209,6 @@
     <t>Luminária</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -899,18 +896,9 @@
     <t>[ 3E.26 ]</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
@@ -942,6 +930,15 @@
   </si>
   <si>
     <t>quem.forneceu</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1384,18 +1381,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1420,17 +1405,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1441,14 +1417,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1477,23 +1447,97 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2171,279 +2215,279 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="B2" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="42" t="s">
+      <c r="B8" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46214.378321643519</v>
-      </c>
-      <c r="C18" s="45" t="s">
+        <v>46216.38845972222</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Lighting</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>98</v>
+      <c r="C24" s="41" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2455,153 +2499,154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="3.84375" customWidth="1"/>
-    <col min="3" max="3" width="7.15234375" customWidth="1"/>
-    <col min="4" max="4" width="9.15234375" customWidth="1"/>
-    <col min="5" max="5" width="10.61328125" customWidth="1"/>
-    <col min="6" max="6" width="10.765625" style="47" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="37" customWidth="1"/>
-    <col min="12" max="12" width="7.69140625" customWidth="1"/>
-    <col min="13" max="13" width="8.84375" customWidth="1"/>
-    <col min="14" max="14" width="10.61328125" customWidth="1"/>
-    <col min="15" max="15" width="11.3828125" customWidth="1"/>
-    <col min="16" max="16" width="30.69140625" customWidth="1"/>
-    <col min="17" max="17" width="29.765625" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.84375" customWidth="1"/>
-    <col min="20" max="20" width="6.15234375" customWidth="1"/>
-    <col min="21" max="21" width="10.15234375" customWidth="1"/>
-    <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.4609375" customWidth="1"/>
-    <col min="24" max="24" width="10.84375" customWidth="1"/>
-    <col min="25" max="25" width="16.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="37" customWidth="1"/>
-    <col min="27" max="27" width="40.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.85546875" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="53" t="s">
+      <c r="M1" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="S1" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y1" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z1" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA1" s="37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="57">
         <v>2</v>
       </c>
-      <c r="J1" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M1" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="S1" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y1" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z1" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" s="41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="32">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>278</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="38" t="s">
+      <c r="E2" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="34" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="34" t="str">
         <f t="shared" si="0"/>
@@ -2609,39 +2654,39 @@
       </c>
       <c r="N2" s="34" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="36" t="str">
+        <v>87</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="30" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="36" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="36" t="str">
+      <c r="U2" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W2" s="69" t="str">
-        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-ILU-",A2)</f>
-        <v>Key-ILU-2</v>
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W2" s="59" t="str">
+        <f>CONCATENATE("Key-ILUM-",A2)</f>
+        <v>Key-ILUM-2</v>
       </c>
       <c r="X2" s="30" t="s">
         <v>9</v>
@@ -2649,51 +2694,51 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="35" t="s">
-        <v>9</v>
+      <c r="Z2" s="30" t="s">
+        <v>288</v>
       </c>
       <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C3" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F3" s="65" t="s">
-        <v>280</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="38" t="s">
+      <c r="E3" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="34" t="str">
         <f t="shared" si="0"/>
@@ -2701,91 +2746,91 @@
       </c>
       <c r="N3" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="36" t="str">
+        <v>87</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="36" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="36" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W3" s="69" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W3" s="59" t="str">
+        <f t="shared" ref="W3:W35" si="4">CONCATENATE("Key-ILUM-",A3)</f>
+        <v>Key-ILUM-3</v>
+      </c>
+      <c r="X3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-ILU-3</v>
-      </c>
-      <c r="X3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="57">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="38" t="s">
+      <c r="E4" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="G4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="34" t="str">
         <f t="shared" si="0"/>
@@ -2793,91 +2838,91 @@
       </c>
       <c r="N4" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="36" t="str">
+        <v>87</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="36" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="36" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W4" s="69" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W4" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-4</v>
+      </c>
+      <c r="X4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-ILU-4</v>
-      </c>
-      <c r="X4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="57">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F5" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="38" t="s">
+      <c r="E5" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="34" t="str">
         <f t="shared" si="0"/>
@@ -2885,91 +2930,91 @@
       </c>
       <c r="N5" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="36" t="str">
+        <v>87</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="36" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="36" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W5" s="69" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W5" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-5</v>
+      </c>
+      <c r="X5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-ILU-5</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>286</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="38" t="s">
+      <c r="E6" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="34" t="str">
         <f t="shared" si="0"/>
@@ -2977,86 +3022,86 @@
       </c>
       <c r="N6" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="36" t="str">
+        <v>87</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="36" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="36" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W6" s="69" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W6" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-6</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>Key-ILU-6</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="30" t="str">
-        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32">
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="57">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C7" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="F7" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="48" t="s">
-        <v>271</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="38" t="s">
+      <c r="G7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="34" t="str">
@@ -3075,79 +3120,79 @@
         <f t="shared" ref="O7:O8" si="8">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
         <v>Circuito.Luz.Geral</v>
       </c>
-      <c r="P7" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q7" s="62" t="s">
+      <c r="P7" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="R7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="T7" s="36" t="str">
+      <c r="Q7" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="R7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="T7" s="30" t="str">
         <f t="shared" ref="T7:T8" si="9">SUBSTITUTE(D7, "_", " ")</f>
         <v>Sistemas.Elétricos</v>
       </c>
-      <c r="U7" s="36" t="str">
+      <c r="U7" s="30" t="str">
         <f t="shared" ref="U7:U8" si="10">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistemas.de.Iluminação</v>
       </c>
-      <c r="V7" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W7" s="69" t="str">
-        <f t="shared" ref="W7:W35" si="11">CONCATENATE("Key-ILU-",A7)</f>
-        <v>Key-ILU-7</v>
-      </c>
-      <c r="X7" s="67" t="s">
+      <c r="V7" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W7" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-7</v>
+      </c>
+      <c r="X7" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y7" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="Y7" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z7" s="35" t="s">
-        <v>274</v>
+      <c r="Z7" s="30" t="s">
+        <v>273</v>
       </c>
       <c r="AA7" s="30" t="str">
-        <f t="shared" ref="AA7:AA8" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <f t="shared" ref="AA7:AA8" si="11">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32">
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="57">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E8" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="E8" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="38" t="s">
+      <c r="F8" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="34" t="str">
@@ -3166,79 +3211,79 @@
         <f t="shared" si="8"/>
         <v>Circuito.Luz.Emergência</v>
       </c>
-      <c r="P8" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q8" s="62" t="s">
+      <c r="P8" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="R8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="T8" s="36" t="str">
+      <c r="Q8" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="T8" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Sistemas.Elétricos</v>
       </c>
-      <c r="U8" s="36" t="str">
+      <c r="U8" s="30" t="str">
         <f t="shared" si="10"/>
         <v>Sistemas.de.Iluminação</v>
       </c>
-      <c r="V8" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W8" s="69" t="str">
+      <c r="V8" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W8" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-8</v>
+      </c>
+      <c r="X8" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y8" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z8" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA8" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>Key-ILU-8</v>
-      </c>
-      <c r="X8" s="67" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y8" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z8" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="AA8" s="30" t="str">
-        <f t="shared" si="12"/>
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="32">
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="57">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E9" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="38" t="s">
+      <c r="F9" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="34" t="str">
@@ -3254,79 +3299,79 @@
         <v>Luminária</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" ref="O9:O35" si="13">IF(ISNUMBER(FIND("Ifc",F9)),CONCATENATE("Classe IFC:   ",F9),CONCATENATE("",F9))</f>
+        <f t="shared" ref="O9:O35" si="12">IF(ISNUMBER(FIND("Ifc",F9)),CONCATENATE("Classe IFC:   ",F9),CONCATENATE("",F9))</f>
         <v>Luz.Aletas</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T9" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U9" s="36" t="s">
+      <c r="T9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U9" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V9" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W9" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-9</v>
+      </c>
+      <c r="X9" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V9" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W9" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-9</v>
-      </c>
-      <c r="X9" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y9" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z9" s="35" t="s">
-        <v>192</v>
+      <c r="Y9" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z9" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="57">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E10" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="50" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="38" t="s">
+      <c r="F10" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="34" t="str">
@@ -3342,79 +3387,79 @@
         <v>Luminária</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">Luz.Antiofuscamento </v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T10" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U10" s="36" t="s">
+      <c r="T10" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U10" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V10" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W10" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-10</v>
+      </c>
+      <c r="X10" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V10" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W10" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-10</v>
-      </c>
-      <c r="X10" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y10" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z10" s="35" t="s">
-        <v>192</v>
+      <c r="Y10" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="32">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E11" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="38" t="s">
+      <c r="F11" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
@@ -3430,79 +3475,79 @@
         <v>Luminária</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Arandela</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T11" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U11" s="36" t="s">
+      <c r="T11" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U11" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V11" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W11" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-11</v>
+      </c>
+      <c r="X11" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V11" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W11" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-11</v>
-      </c>
-      <c r="X11" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y11" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z11" s="35" t="s">
-        <v>192</v>
+      <c r="Y11" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z11" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="57">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="38" t="s">
+      <c r="F12" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="34" t="str">
@@ -3518,79 +3563,79 @@
         <v>Luminária</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Baliza</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="R12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T12" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U12" s="36" t="s">
+      <c r="T12" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U12" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V12" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W12" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-12</v>
+      </c>
+      <c r="X12" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V12" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W12" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-12</v>
-      </c>
-      <c r="X12" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y12" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z12" s="35" t="s">
-        <v>192</v>
+      <c r="Y12" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="57">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="38" t="s">
+      <c r="F13" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="34" t="str">
@@ -3606,79 +3651,79 @@
         <v>Luminária</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Difusa</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T13" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U13" s="36" t="s">
+      <c r="T13" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U13" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V13" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W13" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-13</v>
+      </c>
+      <c r="X13" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V13" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W13" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-13</v>
-      </c>
-      <c r="X13" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y13" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z13" s="35" t="s">
-        <v>192</v>
+      <c r="Y13" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z13" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="57">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="38" t="s">
+      <c r="F14" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
@@ -3694,79 +3739,79 @@
         <v>Luminária</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Embutida.Fixa</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="R14" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T14" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U14" s="36" t="s">
+      <c r="T14" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U14" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V14" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W14" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-14</v>
+      </c>
+      <c r="X14" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V14" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W14" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-14</v>
-      </c>
-      <c r="X14" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y14" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z14" s="35" t="s">
-        <v>192</v>
+      <c r="Y14" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z14" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="57">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E15" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="38" t="s">
+      <c r="F15" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
@@ -3782,167 +3827,167 @@
         <v>Luminária</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Embutida.Orientável</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="R15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T15" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U15" s="36" t="s">
+      <c r="T15" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U15" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V15" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W15" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-15</v>
+      </c>
+      <c r="X15" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V15" s="36" t="s">
+      <c r="Y15" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z15" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA15" s="30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="57">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="34" t="str">
+        <f t="shared" ref="L16" si="13">CONCATENATE("", C16)</f>
+        <v>LuminoTécnico</v>
+      </c>
+      <c r="M16" s="34" t="str">
+        <f t="shared" ref="M16" si="14">CONCATENATE("", D16)</f>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N16" s="34" t="str">
+        <f t="shared" ref="N16" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+        <v>Luminária</v>
+      </c>
+      <c r="O16" s="30" t="str">
+        <f t="shared" ref="O16" si="16">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
+        <v>Luz.Externa</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q16" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="R16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U16" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="W15" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-15</v>
-      </c>
-      <c r="X15" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y15" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z15" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA15" s="30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E16" s="48" t="s">
+      <c r="V16" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W16" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-16</v>
+      </c>
+      <c r="X16" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y16" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z16" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA16" s="30" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="57">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="34" t="str">
-        <f t="shared" ref="L16" si="14">CONCATENATE("", C16)</f>
-        <v>LuminoTécnico</v>
-      </c>
-      <c r="M16" s="34" t="str">
-        <f t="shared" ref="M16" si="15">CONCATENATE("", D16)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N16" s="34" t="str">
-        <f t="shared" ref="N16" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
-        <v>Luminária</v>
-      </c>
-      <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16" si="17">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
-        <v>Luz.Externa</v>
-      </c>
-      <c r="P16" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q16" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="R16" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="T16" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U16" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="V16" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W16" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-16</v>
-      </c>
-      <c r="X16" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y16" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z16" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="38" t="s">
+      <c r="F17" s="63" t="s">
+        <v>260</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
@@ -3958,79 +4003,79 @@
         <v>Luminária</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Externa.Urbana</v>
       </c>
       <c r="P17" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q17" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="R17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T17" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U17" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V17" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W17" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-17</v>
+      </c>
+      <c r="X17" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y17" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z17" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA17" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="Q17" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="R17" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="T17" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U17" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="V17" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W17" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-17</v>
-      </c>
-      <c r="X17" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y17" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z17" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32">
+    </row>
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="57">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E18" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="38" t="s">
+      <c r="F18" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
@@ -4046,79 +4091,79 @@
         <v>Luminária</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Feixe.Amplo</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T18" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U18" s="36" t="s">
+      <c r="T18" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U18" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V18" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W18" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-18</v>
+      </c>
+      <c r="X18" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V18" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W18" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-18</v>
-      </c>
-      <c r="X18" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y18" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z18" s="35" t="s">
-        <v>192</v>
+      <c r="Y18" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z18" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="32">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="57">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E19" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="38" t="s">
+      <c r="F19" s="63" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
@@ -4134,79 +4179,79 @@
         <v>Luminária</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Gôndola</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="R19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T19" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U19" s="36" t="s">
+      <c r="T19" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U19" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V19" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W19" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-19</v>
+      </c>
+      <c r="X19" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V19" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W19" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-19</v>
-      </c>
-      <c r="X19" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y19" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z19" s="35" t="s">
-        <v>192</v>
+      <c r="Y19" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z19" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="32">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="57">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E20" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="38" t="s">
+      <c r="F20" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="34" t="str">
@@ -4222,79 +4267,79 @@
         <v>Luminária</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Grande.Altura</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="R20" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="R20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T20" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U20" s="36" t="s">
+      <c r="T20" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U20" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V20" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W20" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-20</v>
+      </c>
+      <c r="X20" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V20" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W20" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-20</v>
-      </c>
-      <c r="X20" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y20" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z20" s="35" t="s">
-        <v>192</v>
+      <c r="Y20" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z20" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="32">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="57">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E21" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="38" t="s">
+      <c r="F21" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="34" t="str">
@@ -4310,79 +4355,79 @@
         <v>Luminária</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Hermética</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="R21" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="R21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T21" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U21" s="36" t="s">
+      <c r="T21" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U21" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V21" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W21" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-21</v>
+      </c>
+      <c r="X21" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V21" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W21" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-21</v>
-      </c>
-      <c r="X21" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y21" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z21" s="35" t="s">
-        <v>192</v>
+      <c r="Y21" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z21" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="57">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E22" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="38" t="s">
+      <c r="F22" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="34" t="str">
@@ -4398,79 +4443,79 @@
         <v>Luminária</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.LEDFita</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="R22" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="R22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T22" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U22" s="36" t="s">
+      <c r="T22" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U22" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V22" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W22" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-22</v>
+      </c>
+      <c r="X22" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V22" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W22" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-22</v>
-      </c>
-      <c r="X22" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y22" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z22" s="35" t="s">
-        <v>192</v>
+      <c r="Y22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z22" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="57">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E23" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F23" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="38" t="s">
+      <c r="F23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="34" t="str">
@@ -4486,167 +4531,167 @@
         <v>Luminária</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.LEDTubular</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="R23" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U23" s="36" t="s">
+      <c r="T23" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U23" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V23" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W23" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-23</v>
+      </c>
+      <c r="X23" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V23" s="36" t="s">
+      <c r="Y23" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z23" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA23" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="57">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="34" t="str">
+        <f t="shared" ref="L24" si="17">CONCATENATE("", C24)</f>
+        <v>LuminoTécnico</v>
+      </c>
+      <c r="M24" s="34" t="str">
+        <f t="shared" ref="M24" si="18">CONCATENATE("", D24)</f>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N24" s="34" t="str">
+        <f t="shared" ref="N24" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <v>Luminária</v>
+      </c>
+      <c r="O24" s="30" t="str">
+        <f t="shared" ref="O24" si="20">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
+        <v>Luz.TuboFluorescente</v>
+      </c>
+      <c r="P24" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q24" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="R24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T24" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U24" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="W23" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-23</v>
-      </c>
-      <c r="X23" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y23" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z23" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA23" s="30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32">
-        <v>24</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" s="48" t="s">
+      <c r="V24" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W24" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-24</v>
+      </c>
+      <c r="X24" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y24" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z24" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA24" s="30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="57">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="50" t="s">
-        <v>255</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="34" t="str">
-        <f t="shared" ref="L24" si="18">CONCATENATE("", C24)</f>
-        <v>LuminoTécnico</v>
-      </c>
-      <c r="M24" s="34" t="str">
-        <f t="shared" ref="M24" si="19">CONCATENATE("", D24)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N24" s="34" t="str">
-        <f t="shared" ref="N24" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
-        <v>Luminária</v>
-      </c>
-      <c r="O24" s="30" t="str">
-        <f t="shared" ref="O24" si="21">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
-        <v>Luz.TuboFluorescente</v>
-      </c>
-      <c r="P24" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q24" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="R24" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="T24" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U24" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="V24" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W24" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-24</v>
-      </c>
-      <c r="X24" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y24" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z24" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA24" s="30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="38" t="s">
+      <c r="F25" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="34" t="str">
@@ -4662,79 +4707,79 @@
         <v>Luminária</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Linear</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="R25" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="R25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T25" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U25" s="36" t="s">
+      <c r="T25" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U25" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V25" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W25" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-25</v>
+      </c>
+      <c r="X25" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V25" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W25" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-25</v>
-      </c>
-      <c r="X25" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y25" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z25" s="35" t="s">
-        <v>192</v>
+      <c r="Y25" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z25" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="57">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E26" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="38" t="s">
+      <c r="F26" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="34" t="str">
@@ -4750,79 +4795,79 @@
         <v>Luminária</v>
       </c>
       <c r="O26" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Painel</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="R26" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T26" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U26" s="36" t="s">
+      <c r="T26" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U26" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V26" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W26" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-26</v>
+      </c>
+      <c r="X26" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V26" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W26" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-26</v>
-      </c>
-      <c r="X26" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y26" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z26" s="35" t="s">
-        <v>192</v>
+      <c r="Y26" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z26" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="57">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="38" t="s">
+      <c r="F27" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L27" s="34" t="str">
@@ -4838,79 +4883,79 @@
         <v>Luminária</v>
       </c>
       <c r="O27" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Pendente</v>
       </c>
       <c r="P27" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="R27" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T27" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U27" s="36" t="s">
+      <c r="T27" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U27" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V27" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W27" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-27</v>
+      </c>
+      <c r="X27" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V27" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W27" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-27</v>
-      </c>
-      <c r="X27" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y27" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z27" s="35" t="s">
-        <v>192</v>
+      <c r="Y27" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z27" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="57">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E28" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F28" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="38" t="s">
+      <c r="F28" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L28" s="34" t="str">
@@ -4926,79 +4971,79 @@
         <v>Luminária</v>
       </c>
       <c r="O28" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Plafon</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q28" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="R28" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T28" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U28" s="36" t="s">
+      <c r="T28" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U28" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V28" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W28" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-28</v>
+      </c>
+      <c r="X28" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V28" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W28" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-28</v>
-      </c>
-      <c r="X28" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y28" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z28" s="35" t="s">
-        <v>192</v>
+      <c r="Y28" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z28" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="57">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E29" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F29" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="G29" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="38" t="s">
+      <c r="F29" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="G29" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L29" s="34" t="str">
@@ -5014,79 +5059,79 @@
         <v>Luminária</v>
       </c>
       <c r="O29" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Sensorizada</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="R29" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T29" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U29" s="36" t="s">
+      <c r="T29" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U29" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V29" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W29" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-29</v>
+      </c>
+      <c r="X29" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V29" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W29" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-29</v>
-      </c>
-      <c r="X29" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y29" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z29" s="35" t="s">
-        <v>192</v>
+      <c r="Y29" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z29" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA29" s="30" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="57">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E30" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E30" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F30" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="G30" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="38" t="s">
+      <c r="F30" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L30" s="34" t="str">
@@ -5102,79 +5147,79 @@
         <v>Luminária</v>
       </c>
       <c r="O30" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Spot</v>
       </c>
       <c r="P30" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q30" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="R30" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T30" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U30" s="36" t="s">
+      <c r="T30" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U30" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V30" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W30" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-30</v>
+      </c>
+      <c r="X30" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V30" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W30" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-30</v>
-      </c>
-      <c r="X30" s="36" t="s">
+      <c r="Y30" s="62" t="s">
         <v>252</v>
       </c>
-      <c r="Y30" s="67" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z30" s="35" t="s">
-        <v>192</v>
+      <c r="Z30" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="32">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="57">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E31" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F31" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="G31" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="38" t="s">
+      <c r="F31" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L31" s="34" t="str">
@@ -5190,167 +5235,167 @@
         <v>Luminária</v>
       </c>
       <c r="O31" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Luz.Trilho</v>
       </c>
       <c r="P31" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q31" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="R31" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T31" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U31" s="36" t="s">
+      <c r="T31" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U31" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="V31" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W31" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-31</v>
+      </c>
+      <c r="X31" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="V31" s="36" t="s">
+      <c r="Y31" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z31" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA31" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="57">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="F32" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="34" t="str">
+        <f t="shared" ref="L32" si="21">CONCATENATE("", C32)</f>
+        <v>LuminoTécnico</v>
+      </c>
+      <c r="M32" s="34" t="str">
+        <f t="shared" ref="M32" si="22">CONCATENATE("", D32)</f>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N32" s="34" t="str">
+        <f t="shared" ref="N32" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
+        <v>Acessórios de Iluminação</v>
+      </c>
+      <c r="O32" s="30" t="str">
+        <f t="shared" ref="O32" si="24">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("Classe IFC:   ",F32),CONCATENATE("",F32))</f>
+        <v>Acessório.Luz</v>
+      </c>
+      <c r="P32" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q32" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="R32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T32" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U32" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="W31" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-31</v>
-      </c>
-      <c r="X31" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y31" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z31" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA31" s="30" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32">
-        <v>32</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="V32" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W32" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-32</v>
+      </c>
+      <c r="X32" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y32" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z32" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA32" s="30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="57">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="E32" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="F32" s="50" t="s">
-        <v>254</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L32" s="34" t="str">
-        <f t="shared" ref="L32" si="22">CONCATENATE("", C32)</f>
-        <v>LuminoTécnico</v>
-      </c>
-      <c r="M32" s="34" t="str">
-        <f t="shared" ref="M32" si="23">CONCATENATE("", D32)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N32" s="34" t="str">
-        <f t="shared" ref="N32" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
-        <v>Acessórios de Iluminação</v>
-      </c>
-      <c r="O32" s="30" t="str">
-        <f t="shared" ref="O32" si="25">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("Classe IFC:   ",F32),CONCATENATE("",F32))</f>
-        <v>Acessório.Luz</v>
-      </c>
-      <c r="P32" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q32" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="R32" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="T32" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="U32" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="V32" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W32" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-32</v>
-      </c>
-      <c r="X32" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y32" s="67" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z32" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA32" s="30" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="32">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E33" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="F33" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="G33" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="38" t="s">
+      <c r="F33" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L33" s="34" t="str">
@@ -5366,79 +5411,79 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O33" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Ponto.Iluminado</v>
       </c>
       <c r="P33" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q33" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="R33" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T33" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="U33" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="V33" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W33" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-33</v>
-      </c>
-      <c r="X33" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y33" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z33" s="35" t="s">
+      <c r="T33" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="U33" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="V33" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W33" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-33</v>
+      </c>
+      <c r="X33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="32">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="57">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E34" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="F34" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="38" t="s">
+      <c r="F34" s="63" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="34" t="str">
@@ -5454,79 +5499,79 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O34" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Linha.Iluminada</v>
       </c>
       <c r="P34" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="R34" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="R34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S34" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T34" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="U34" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="V34" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W34" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-34</v>
-      </c>
-      <c r="X34" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y34" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z34" s="35" t="s">
+      <c r="T34" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="U34" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="V34" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W34" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-34</v>
+      </c>
+      <c r="X34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="32">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="57">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>197</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="38" t="s">
+      <c r="F35" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L35" s="34" t="str">
@@ -5542,45 +5587,45 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O35" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Area.Iluminada</v>
       </c>
       <c r="P35" s="30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="R35" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="R35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S35" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T35" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="U35" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="V35" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="W35" s="69" t="str">
-        <f t="shared" si="11"/>
-        <v>Key-ILU-35</v>
-      </c>
-      <c r="X35" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y35" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z35" s="35" t="s">
+      <c r="T35" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="U35" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="V35" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="W35" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-ILUM-35</v>
+      </c>
+      <c r="X35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -5588,56 +5633,56 @@
     <sortCondition ref="F7:F929"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A35">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA9:AA35">
-    <cfRule type="cellIs" dxfId="24" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1479"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="duplicateValues" dxfId="18" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31 F33:F35">
-    <cfRule type="duplicateValues" dxfId="16" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36:F1048576 F9:F30">
-    <cfRule type="duplicateValues" dxfId="14" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1451"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:X32">
-    <cfRule type="containsText" dxfId="11" priority="37" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y30">
-    <cfRule type="duplicateValues" dxfId="10" priority="34"/>
-    <cfRule type="containsText" dxfId="9" priority="35" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="16" priority="40"/>
+    <cfRule type="containsText" dxfId="15" priority="41" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y30)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B35">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5649,15 +5694,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5722,7 +5767,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5787,7 +5832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5854,7 +5899,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5870,853 +5915,853 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="59" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.4609375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.23046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.07421875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.4609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="58" t="s">
-        <v>79</v>
-      </c>
       <c r="I1" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>278</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="H2" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="J2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="L2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="59" t="s">
+      <c r="P2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="59" t="s">
+      <c r="R2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>2</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="64" t="s">
-        <v>185</v>
+        <v>221</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>184</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="H3" s="59" t="s">
-        <v>80</v>
+        <v>226</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>79</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="J3" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="J3" s="50" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="50" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="50" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="59" t="s">
-        <v>213</v>
+      <c r="P3" s="50" t="s">
+        <v>212</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="R3" s="59" t="s">
-        <v>216</v>
+        <v>232</v>
+      </c>
+      <c r="R3" s="50" t="s">
+        <v>215</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>3</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>185</v>
+        <v>222</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>184</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="H4" s="59" t="s">
-        <v>80</v>
+        <v>226</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>79</v>
       </c>
       <c r="I4" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="J4" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="R4" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S4" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="J4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="R4" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>4</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="59" t="s">
-        <v>80</v>
+      <c r="H5" s="50" t="s">
+        <v>79</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="J5" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="J5" s="50" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="59" t="s">
+      <c r="L5" s="50" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="59" t="s">
+      <c r="N5" s="50" t="s">
         <v>9</v>
       </c>
       <c r="O5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="59" t="s">
-        <v>213</v>
+      <c r="P5" s="50" t="s">
+        <v>212</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="R5" s="59" t="s">
-        <v>216</v>
+        <v>232</v>
+      </c>
+      <c r="R5" s="50" t="s">
+        <v>215</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q6" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="J6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="R6" s="59" t="s">
-        <v>216</v>
+      <c r="R6" s="50" t="s">
+        <v>215</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="64" t="s">
-        <v>232</v>
+      <c r="B7" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>231</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H7" s="59" t="s">
-        <v>288</v>
+        <v>187</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J7" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="K7" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L7" s="59" t="s">
-        <v>289</v>
+      <c r="L7" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N7" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O7" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O7" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P7" s="59" t="s">
+      <c r="P7" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="R7" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S7" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R7" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>7</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>232</v>
+      <c r="B8" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>231</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H8" s="59" t="s">
-        <v>288</v>
+        <v>187</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J8" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="K8" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L8" s="59" t="s">
-        <v>289</v>
+      <c r="L8" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N8" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N8" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O8" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O8" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" s="59" t="s">
+      <c r="P8" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q8" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="R8" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S8" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R8" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>8</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="J9" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="N9" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="P9" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="R9" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S9" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21">
+        <v>9</v>
+      </c>
+      <c r="B10" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="64" t="s">
-        <v>232</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H9" s="59" t="s">
-        <v>288</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J9" s="59" t="s">
+      <c r="C10" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="K9" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L9" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N9" s="59" t="s">
+      <c r="L10" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="N10" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O10" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O9" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P9" s="59" t="s">
+      <c r="P10" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q10" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q9" s="25" t="s">
+      <c r="R10" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S10" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R9" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21">
-        <v>9</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="59" t="s">
-        <v>288</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J10" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L10" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="O10" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P10" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q10" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>10</v>
       </c>
-      <c r="B11" s="57" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="64" t="s">
-        <v>231</v>
+      <c r="B11" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>230</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" s="59" t="s">
-        <v>288</v>
+        <v>188</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" s="59" t="s">
-        <v>228</v>
+        <v>185</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>227</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="L11" s="59" t="s">
-        <v>289</v>
+        <v>229</v>
+      </c>
+      <c r="L11" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N11" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O11" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O11" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P11" s="59" t="s">
+      <c r="P11" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q11" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="R11" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S11" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R11" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S11" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>231</v>
+      <c r="B12" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>230</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H12" s="59" t="s">
-        <v>288</v>
+        <v>188</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J12" s="59" t="s">
-        <v>228</v>
+        <v>185</v>
+      </c>
+      <c r="J12" s="50" t="s">
+        <v>227</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="L12" s="59" t="s">
-        <v>289</v>
+        <v>229</v>
+      </c>
+      <c r="L12" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N12" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N12" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O12" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O12" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P12" s="59" t="s">
+      <c r="P12" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q12" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="R12" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S12" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R12" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S12" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>12</v>
       </c>
-      <c r="B13" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="64" t="s">
-        <v>231</v>
+      <c r="B13" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="55" t="s">
+        <v>230</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H13" s="59" t="s">
-        <v>288</v>
+        <v>188</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" s="59" t="s">
-        <v>228</v>
+        <v>185</v>
+      </c>
+      <c r="J13" s="50" t="s">
+        <v>227</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="L13" s="59" t="s">
-        <v>289</v>
+        <v>229</v>
+      </c>
+      <c r="L13" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N13" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O13" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O13" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P13" s="59" t="s">
+      <c r="P13" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q13" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q13" s="25" t="s">
+      <c r="R13" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S13" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="R13" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S13" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>231</v>
+      <c r="B14" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>230</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H14" s="59" t="s">
-        <v>288</v>
+        <v>188</v>
+      </c>
+      <c r="H14" s="50" t="s">
+        <v>284</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" s="59" t="s">
-        <v>228</v>
+        <v>185</v>
+      </c>
+      <c r="J14" s="50" t="s">
+        <v>227</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="L14" s="59" t="s">
-        <v>289</v>
+        <v>229</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>285</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="N14" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="N14" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="O14" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="O14" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="P14" s="59" t="s">
+      <c r="P14" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q14" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="Q14" s="25" t="s">
+      <c r="R14" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="S14" s="25" t="s">
         <v>214</v>
-      </c>
-      <c r="R14" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S14" s="25" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -6729,38 +6774,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.921875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.23046875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="D1" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="29" t="s">
-        <v>84</v>
-      </c>
       <c r="E1" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6789,22 +6834,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ILUM/Ontologia_Iluminação.xlsx
+++ b/Versão5/ILUM/Ontologia_Iluminação.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9386F8-C92F-4BEA-AE5C-AF498A1F64A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB9F94-B7F7-4D03-8A15-AC079F918142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -875,9 +875,6 @@
     <t>Luminaria de Exteriores Domésticos como patios y jardines</t>
   </si>
   <si>
-    <t>LuminoTécnico</t>
-  </si>
-  <si>
     <t>Circuito.Luz.Geral</t>
   </si>
   <si>
@@ -932,13 +929,16 @@
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>LuminoTécnicos</t>
   </si>
 </sst>
 </file>
@@ -1481,63 +1481,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -2215,14 +2159,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="33.69140625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2233,7 +2177,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2244,7 +2188,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2255,7 +2199,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2266,7 +2210,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2278,7 +2222,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2290,7 +2234,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2301,7 +2245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2312,7 +2256,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2323,7 +2267,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2334,7 +2278,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2345,7 +2289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2356,7 +2300,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2367,7 +2311,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2378,7 +2322,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2389,7 +2333,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2400,7 +2344,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2411,19 +2355,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46216.38845972222</v>
+        <v>46243.523988078705</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2434,7 +2378,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2445,7 +2389,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2456,7 +2400,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2467,7 +2411,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2478,7 +2422,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>93</v>
       </c>
@@ -2499,35 +2443,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="65" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3828125" style="65" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8" style="60" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.85546875" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="60"/>
+    <col min="12" max="12" width="8.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.84375" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>159</v>
       </c>
@@ -2610,21 +2554,21 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F2" s="56" t="s">
         <v>85</v>
@@ -2661,7 +2605,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>87</v>
@@ -2695,31 +2639,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G3" s="58" t="s">
         <v>9</v>
@@ -2753,7 +2697,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>87</v>
@@ -2794,24 +2738,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>9</v>
@@ -2845,7 +2789,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>87</v>
@@ -2886,24 +2830,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>9</v>
@@ -2937,7 +2881,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>87</v>
@@ -2978,24 +2922,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>9</v>
@@ -3029,7 +2973,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>87</v>
@@ -3070,24 +3014,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="F7" s="43" t="s">
         <v>267</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>268</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>9</v>
@@ -3106,7 +3050,7 @@
       </c>
       <c r="L7" s="34" t="str">
         <f t="shared" ref="L7:L35" si="5">CONCATENATE("", C7)</f>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M7" s="34" t="str">
         <f t="shared" ref="M7:M35" si="6">CONCATENATE("", D7)</f>
@@ -3130,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T7" s="30" t="str">
         <f t="shared" ref="T7:T8" si="9">SUBSTITUTE(D7, "_", " ")</f>
@@ -3154,31 +3098,31 @@
         <v>219</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA7" s="30" t="str">
         <f t="shared" ref="AA7:AA8" si="11">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D8" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="43" t="s">
-        <v>271</v>
-      </c>
       <c r="F8" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>9</v>
@@ -3197,7 +3141,7 @@
       </c>
       <c r="L8" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M8" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3221,7 +3165,7 @@
         <v>9</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T8" s="30" t="str">
         <f t="shared" si="9"/>
@@ -3245,22 +3189,22 @@
         <v>219</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA8" s="30" t="str">
         <f t="shared" si="11"/>
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>245</v>
@@ -3288,7 +3232,7 @@
       </c>
       <c r="L9" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M9" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3340,15 +3284,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>245</v>
@@ -3376,7 +3320,7 @@
       </c>
       <c r="L10" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M10" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3428,15 +3372,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>245</v>
@@ -3464,7 +3408,7 @@
       </c>
       <c r="L11" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M11" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3516,15 +3460,15 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>245</v>
@@ -3552,7 +3496,7 @@
       </c>
       <c r="L12" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M12" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3604,15 +3548,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>245</v>
@@ -3640,7 +3584,7 @@
       </c>
       <c r="L13" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M13" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3692,15 +3636,15 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>245</v>
@@ -3728,7 +3672,7 @@
       </c>
       <c r="L14" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M14" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3780,15 +3724,15 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>245</v>
@@ -3816,7 +3760,7 @@
       </c>
       <c r="L15" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M15" s="34" t="str">
         <f t="shared" si="6"/>
@@ -3868,15 +3812,15 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>245</v>
@@ -3904,7 +3848,7 @@
       </c>
       <c r="L16" s="34" t="str">
         <f t="shared" ref="L16" si="13">CONCATENATE("", C16)</f>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M16" s="34" t="str">
         <f t="shared" ref="M16" si="14">CONCATENATE("", D16)</f>
@@ -3956,15 +3900,15 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="57">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>245</v>
@@ -3992,7 +3936,7 @@
       </c>
       <c r="L17" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M17" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4044,15 +3988,15 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="57">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>245</v>
@@ -4080,7 +4024,7 @@
       </c>
       <c r="L18" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M18" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4132,15 +4076,15 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="57">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>245</v>
@@ -4168,7 +4112,7 @@
       </c>
       <c r="L19" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M19" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4220,15 +4164,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="57">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>245</v>
@@ -4256,7 +4200,7 @@
       </c>
       <c r="L20" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M20" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4308,15 +4252,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>245</v>
@@ -4344,7 +4288,7 @@
       </c>
       <c r="L21" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M21" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4396,15 +4340,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>245</v>
@@ -4432,7 +4376,7 @@
       </c>
       <c r="L22" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M22" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4484,15 +4428,15 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="57">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>245</v>
@@ -4520,7 +4464,7 @@
       </c>
       <c r="L23" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M23" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4572,15 +4516,15 @@
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>245</v>
@@ -4608,7 +4552,7 @@
       </c>
       <c r="L24" s="34" t="str">
         <f t="shared" ref="L24" si="17">CONCATENATE("", C24)</f>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M24" s="34" t="str">
         <f t="shared" ref="M24" si="18">CONCATENATE("", D24)</f>
@@ -4660,15 +4604,15 @@
         <v>257</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="57">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>245</v>
@@ -4696,7 +4640,7 @@
       </c>
       <c r="L25" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M25" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4748,15 +4692,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="57">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>245</v>
@@ -4784,7 +4728,7 @@
       </c>
       <c r="L26" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M26" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4836,15 +4780,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="57">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>245</v>
@@ -4872,7 +4816,7 @@
       </c>
       <c r="L27" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M27" s="34" t="str">
         <f t="shared" si="6"/>
@@ -4924,15 +4868,15 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="57">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>245</v>
@@ -4960,7 +4904,7 @@
       </c>
       <c r="L28" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M28" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5012,15 +4956,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="57">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>245</v>
@@ -5048,7 +4992,7 @@
       </c>
       <c r="L29" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M29" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5100,15 +5044,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="57">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>245</v>
@@ -5136,7 +5080,7 @@
       </c>
       <c r="L30" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M30" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5188,15 +5132,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="57">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>245</v>
@@ -5224,7 +5168,7 @@
       </c>
       <c r="L31" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M31" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5276,15 +5220,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="57">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>245</v>
@@ -5312,7 +5256,7 @@
       </c>
       <c r="L32" s="34" t="str">
         <f t="shared" ref="L32" si="21">CONCATENATE("", C32)</f>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M32" s="34" t="str">
         <f t="shared" ref="M32" si="22">CONCATENATE("", D32)</f>
@@ -5364,15 +5308,15 @@
         <v>258</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="57">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>245</v>
@@ -5400,7 +5344,7 @@
       </c>
       <c r="L33" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M33" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5452,15 +5396,15 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="57">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>245</v>
@@ -5488,7 +5432,7 @@
       </c>
       <c r="L34" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M34" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5540,15 +5484,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="57">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>245</v>
@@ -5576,7 +5520,7 @@
       </c>
       <c r="L35" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>LuminoTécnico</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M35" s="34" t="str">
         <f t="shared" si="6"/>
@@ -5633,56 +5577,56 @@
     <sortCondition ref="F7:F929"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:B35">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA9:AA35">
-    <cfRule type="cellIs" dxfId="30" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="29" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1485"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="duplicateValues" dxfId="24" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="1478"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31 F33:F35">
-    <cfRule type="duplicateValues" dxfId="22" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36:F1048576 F9:F30">
-    <cfRule type="duplicateValues" dxfId="20" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1457"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:X32">
-    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="43" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y30">
-    <cfRule type="duplicateValues" dxfId="16" priority="40"/>
-    <cfRule type="containsText" dxfId="15" priority="41" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
+    <cfRule type="containsText" dxfId="9" priority="41" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y30)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="14" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B35">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5694,15 +5638,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5767,7 +5711,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5832,7 +5776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5899,7 +5843,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5915,30 +5859,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="80.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="80.3046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5997,7 +5941,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -6056,7 +6000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -6064,7 +6008,7 @@
         <v>221</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D3" s="51" t="s">
         <v>84</v>
@@ -6115,7 +6059,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>3</v>
       </c>
@@ -6123,7 +6067,7 @@
         <v>222</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D4" s="51" t="s">
         <v>84</v>
@@ -6174,7 +6118,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>4</v>
       </c>
@@ -6182,7 +6126,7 @@
         <v>230</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D5" s="51" t="s">
         <v>223</v>
@@ -6233,7 +6177,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -6241,7 +6185,7 @@
         <v>231</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D6" s="51" t="s">
         <v>223</v>
@@ -6292,7 +6236,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>6</v>
       </c>
@@ -6315,7 +6259,7 @@
         <v>187</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>185</v>
@@ -6327,7 +6271,7 @@
         <v>228</v>
       </c>
       <c r="L7" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M7" s="25" t="s">
         <v>208</v>
@@ -6351,7 +6295,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>7</v>
       </c>
@@ -6374,7 +6318,7 @@
         <v>187</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>185</v>
@@ -6386,7 +6330,7 @@
         <v>228</v>
       </c>
       <c r="L8" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M8" s="25" t="s">
         <v>208</v>
@@ -6410,7 +6354,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>8</v>
       </c>
@@ -6433,7 +6377,7 @@
         <v>187</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>185</v>
@@ -6445,7 +6389,7 @@
         <v>228</v>
       </c>
       <c r="L9" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M9" s="25" t="s">
         <v>208</v>
@@ -6469,7 +6413,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>9</v>
       </c>
@@ -6492,7 +6436,7 @@
         <v>187</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>185</v>
@@ -6504,7 +6448,7 @@
         <v>228</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M10" s="25" t="s">
         <v>208</v>
@@ -6528,7 +6472,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>10</v>
       </c>
@@ -6551,7 +6495,7 @@
         <v>188</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I11" s="25" t="s">
         <v>185</v>
@@ -6563,7 +6507,7 @@
         <v>229</v>
       </c>
       <c r="L11" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M11" s="25" t="s">
         <v>208</v>
@@ -6587,7 +6531,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>11</v>
       </c>
@@ -6610,7 +6554,7 @@
         <v>188</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I12" s="25" t="s">
         <v>185</v>
@@ -6622,7 +6566,7 @@
         <v>229</v>
       </c>
       <c r="L12" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M12" s="25" t="s">
         <v>208</v>
@@ -6646,7 +6590,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -6669,7 +6613,7 @@
         <v>188</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I13" s="25" t="s">
         <v>185</v>
@@ -6681,7 +6625,7 @@
         <v>229</v>
       </c>
       <c r="L13" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M13" s="25" t="s">
         <v>208</v>
@@ -6705,7 +6649,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>13</v>
       </c>
@@ -6728,7 +6672,7 @@
         <v>188</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>185</v>
@@ -6740,7 +6684,7 @@
         <v>229</v>
       </c>
       <c r="L14" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M14" s="25" t="s">
         <v>208</v>
@@ -6774,15 +6718,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6805,7 +6749,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6834,22 +6778,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="10" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ILUM/Ontologia_Iluminação.xlsx
+++ b/Versão5/ILUM/Ontologia_Iluminação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB9F94-B7F7-4D03-8A15-AC079F918142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BE782C-F0AF-40EB-A009-B3EC98685FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="274">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -327,15 +327,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>CategoriaRvt</t>
   </si>
   <si>
@@ -560,12 +551,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>[ IfcLamp , IfcLightFixture ]</t>
-  </si>
-  <si>
-    <t>[ IfcLamp , IfcLampLED ]</t>
-  </si>
-  <si>
     <t>Fin Luminaire</t>
   </si>
   <si>
@@ -632,9 +617,6 @@
     <t>"Lumicenter Lighting"</t>
   </si>
   <si>
-    <t>"Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
-  </si>
-  <si>
     <t>"Indivíduo Luminária arandela, ideal para criar efeitos de luz decorativos em ambientes residenciais, hotéis, bares e restaurantes."</t>
   </si>
   <si>
@@ -713,12 +695,6 @@
     <t>classe.ifc</t>
   </si>
   <si>
-    <t>"IfcLamp"</t>
-  </si>
-  <si>
-    <t>"OST_LightingDevices"</t>
-  </si>
-  <si>
     <t>categoria.revit</t>
   </si>
   <si>
@@ -770,9 +746,6 @@
     <t>Lumi_Sala_A</t>
   </si>
   <si>
-    <t>"IfcDistributionSystemLIGHTING"</t>
-  </si>
-  <si>
     <t>Lum_333324</t>
   </si>
   <si>
@@ -803,9 +776,6 @@
     <t>"Circuito de iluminação 2"</t>
   </si>
   <si>
-    <t>"OST_SwitchSystem"</t>
-  </si>
-  <si>
     <t>[ IfcDiscreteAccessory ]</t>
   </si>
   <si>
@@ -830,9 +800,6 @@
     <t>[ OST_LightingFixtures ]</t>
   </si>
   <si>
-    <t>[ IfcLamp , IfcLightFixturePOINTSOURCE ]</t>
-  </si>
-  <si>
     <t>Acessório.Luz</t>
   </si>
   <si>
@@ -893,52 +860,40 @@
     <t>[ 3E.26 ]</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>quem.fabricou</t>
   </si>
   <si>
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
-  </si>
-  <si>
     <t>Conceitos</t>
   </si>
   <si>
     <t>LuminoTécnicos</t>
+  </si>
+  <si>
+    <t>[ IfcLamp : IfcLightFixture ]</t>
+  </si>
+  <si>
+    <t>[ IfcLamp : IfcLampLED ]</t>
+  </si>
+  <si>
+    <t>[ IfcLamp : IfcLightFixturePOINTSOURCE ]</t>
+  </si>
+  <si>
+    <t>"Informações contidas no Projeto de Luminotécnica"</t>
+  </si>
+  <si>
+    <t>"[ IfcDistributionSystemLIGHTING ]"</t>
+  </si>
+  <si>
+    <t>"[ IfcLamp ]"</t>
+  </si>
+  <si>
+    <t>"[ OST_SwitchSystem ]"</t>
+  </si>
+  <si>
+    <t>"[ OST_LightingDevices ]"</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1444,9 +1399,6 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1481,7 +1433,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
@@ -1548,14 +1500,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1589,46 +1533,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2159,14 +2063,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2174,10 +2078,10 @@
         <v>47</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2185,21 +2089,21 @@
         <v>49</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2207,10 +2111,10 @@
         <v>32</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2219,10 +2123,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2231,10 +2135,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2242,21 +2146,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2264,10 +2168,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2275,10 +2179,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2286,10 +2190,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2297,10 +2201,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2308,10 +2212,10 @@
         <v>60</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2319,10 +2223,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2330,10 +2234,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2341,33 +2245,33 @@
         <v>60</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46243.523988078705</v>
+        <v>46244.669257175927</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2375,10 +2279,10 @@
         <v>70</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2386,10 +2290,10 @@
         <v>60</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2397,41 +2301,41 @@
         <v>60</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Lighting</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2442,38 +2346,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AA30"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3828125" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="60" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.3828125" style="60" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.84375" style="60" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.3828125" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.84375" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.84375" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="60"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.85546875" style="65" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B1" s="45" t="s">
         <v>42</v>
@@ -2506,7 +2410,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="M1" s="36" t="s">
         <v>5</v>
@@ -2524,7 +2428,7 @@
         <v>43</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S1" s="36" t="s">
         <v>33</v>
@@ -2538,719 +2442,699 @@
       <c r="V1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="61" t="s">
+      <c r="W1" s="60" t="s">
         <v>8</v>
       </c>
       <c r="X1" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y1" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z1" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="Y1" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z1" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA1" s="37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="57">
+    </row>
+    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="34" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
+        <f t="shared" ref="L2:L30" si="0">CONCATENATE("", C2)</f>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M2" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" ref="M2:M30" si="1">CONCATENATE("", D2)</f>
+        <v>Sistemas.Elétricos</v>
       </c>
       <c r="N2" s="34" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
-      </c>
-      <c r="O2" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>87</v>
+        <f t="shared" ref="N2:N30" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Sistemas de Iluminação</v>
+      </c>
+      <c r="O2" s="30" t="str">
+        <f t="shared" ref="O2:O3" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
+        <v>Circuito.Luz.Geral</v>
+      </c>
+      <c r="P2" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>208</v>
       </c>
       <c r="R2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="30" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
+      <c r="S2" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="T2" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" ref="T2:T3" si="4">SUBSTITUTE(D2, "_", " ")</f>
+        <v>Sistemas.Elétricos</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" ref="U2:U3" si="5">SUBSTITUTE(E2, "_", " ")</f>
+        <v>Sistemas.de.Iluminação</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W2" s="59" t="str">
-        <f>CONCATENATE("Key-ILUM-",A2)</f>
+        <v>239</v>
+      </c>
+      <c r="W2" s="58" t="str">
+        <f t="shared" ref="W2:W30" si="6">CONCATENATE("Key-ILUM-",A2)</f>
         <v>Key-ILUM-2</v>
       </c>
-      <c r="X2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="30" t="s">
-        <v>9</v>
+      <c r="X2" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y2" s="61" t="s">
+        <v>211</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="57">
+        <f t="shared" ref="AA2:AA3" si="7">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Electrical Lighting System</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M3" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="1"/>
+        <v>Sistemas.Elétricos</v>
       </c>
       <c r="N3" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O3" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
-      </c>
-      <c r="P3" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>87</v>
+        <f t="shared" si="2"/>
+        <v>Sistemas de Iluminação</v>
+      </c>
+      <c r="O3" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Circuito.Luz.Emergência</v>
+      </c>
+      <c r="P3" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q3" s="53" t="s">
+        <v>208</v>
       </c>
       <c r="R3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
+      <c r="S3" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="T3" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
+        <f t="shared" si="4"/>
+        <v>Sistemas.Elétricos</v>
       </c>
       <c r="U3" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="5"/>
+        <v>Sistemas.de.Iluminação</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W3" s="59" t="str">
-        <f t="shared" ref="W3:W35" si="4">CONCATENATE("Key-ILUM-",A3)</f>
+        <v>239</v>
+      </c>
+      <c r="W3" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-3</v>
       </c>
-      <c r="X3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>9</v>
+      <c r="X3" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y3" s="61" t="s">
+        <v>211</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="AA3" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="57">
+        <f t="shared" si="7"/>
+        <v>Electrical Lighting System</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>265</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="G4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M4" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="1"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N4" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O4" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
+        <f t="shared" si="2"/>
+        <v>Luminária</v>
+      </c>
+      <c r="O4" s="30" t="str">
+        <f t="shared" ref="O4:O30" si="8">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
+        <v>Luz.Aletas</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="R4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T4" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+      <c r="S4" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U4" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W4" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W4" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-4</v>
       </c>
       <c r="X4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>9</v>
+        <v>241</v>
+      </c>
+      <c r="Y4" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="57">
+        <v>185</v>
+      </c>
+      <c r="AA4" s="30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>265</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M5" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="1"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N5" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O5" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
+        <f t="shared" si="2"/>
+        <v>Luminária</v>
+      </c>
+      <c r="O5" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Luz.Antiofuscamento </v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="R5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T5" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+      <c r="S5" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U5" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W5" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W5" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-5</v>
       </c>
       <c r="X5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>9</v>
+        <v>241</v>
+      </c>
+      <c r="Y5" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="57">
+        <v>185</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>265</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="F6" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="G6" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M6" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N6" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>Luminária</v>
+      </c>
+      <c r="O6" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Luz.Arandela</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U6" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="W6" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-6</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y6" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z6" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="56">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N6" s="34" t="str">
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M7" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O6" s="34" t="str">
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N7" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>Luminária</v>
+      </c>
+      <c r="O7" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Luz.Baliza</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="R7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U7" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="V7" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="W7" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-7</v>
+      </c>
+      <c r="X7" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y7" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z7" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA7" s="30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="56">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M8" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="R6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="30" t="str">
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N8" s="34" t="str">
         <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T6" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U6" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W6" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-6</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="57">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="34" t="str">
-        <f t="shared" ref="L7:L35" si="5">CONCATENATE("", C7)</f>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M7" s="34" t="str">
-        <f t="shared" ref="M7:M35" si="6">CONCATENATE("", D7)</f>
-        <v>Sistemas.Elétricos</v>
-      </c>
-      <c r="N7" s="34" t="str">
-        <f t="shared" ref="N7:N35" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
-        <v>Sistemas de Iluminação</v>
-      </c>
-      <c r="O7" s="30" t="str">
-        <f t="shared" ref="O7:O8" si="8">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
-        <v>Circuito.Luz.Geral</v>
-      </c>
-      <c r="P7" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q7" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="R7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="T7" s="30" t="str">
-        <f t="shared" ref="T7:T8" si="9">SUBSTITUTE(D7, "_", " ")</f>
-        <v>Sistemas.Elétricos</v>
-      </c>
-      <c r="U7" s="30" t="str">
-        <f t="shared" ref="U7:U8" si="10">SUBSTITUTE(E7, "_", " ")</f>
-        <v>Sistemas.de.Iluminação</v>
-      </c>
-      <c r="V7" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W7" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-7</v>
-      </c>
-      <c r="X7" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y7" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z7" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA7" s="30" t="str">
-        <f t="shared" ref="AA7:AA8" si="11">_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Electrical Lighting System</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="57">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>268</v>
-      </c>
-      <c r="G8" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M8" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Elétricos</v>
-      </c>
-      <c r="N8" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas de Iluminação</v>
+        <v>Luminária</v>
       </c>
       <c r="O8" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Circuito.Luz.Emergência</v>
-      </c>
-      <c r="P8" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q8" s="53" t="s">
-        <v>216</v>
+        <v>Luz.Difusa</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="T8" s="30" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistemas.Elétricos</v>
-      </c>
-      <c r="U8" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Sistemas.de.Iluminação</v>
+        <v>44</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U8" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W8" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W8" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-8</v>
       </c>
-      <c r="X8" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y8" s="62" t="s">
-        <v>219</v>
+      <c r="X8" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y8" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA8" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>Electrical Lighting System</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="57">
+        <v>185</v>
+      </c>
+      <c r="AA8" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="56">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E9" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="58" t="s">
+      <c r="G9" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M9" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N9" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" ref="O9:O35" si="12">IF(ISNUMBER(FIND("Ifc",F9)),CONCATENATE("Classe IFC:   ",F9),CONCATENATE("",F9))</f>
-        <v>Luz.Aletas</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Embutida.Fixa</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>9</v>
@@ -3259,86 +3143,86 @@
         <v>44</v>
       </c>
       <c r="T9" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U9" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W9" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W9" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-9</v>
       </c>
       <c r="X9" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y9" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y9" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA9" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="57">
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E10" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="58" t="s">
+      <c r="F10" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M10" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N10" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">Luz.Antiofuscamento </v>
+        <f t="shared" si="8"/>
+        <v>Luz.Embutida.Orientável</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
@@ -3347,86 +3231,86 @@
         <v>44</v>
       </c>
       <c r="T10" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U10" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W10" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W10" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-10</v>
       </c>
       <c r="X10" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y10" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y10" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA10" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="57">
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="56">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E11" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="58" t="s">
+      <c r="F11" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L11" si="9">CONCATENATE("", C11)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M11" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="M11" si="10">CONCATENATE("", D11)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N11" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="N11" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Luminária</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Arandela</v>
+        <f t="shared" ref="O11" si="12">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
+        <v>Luz.Externa</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>121</v>
+        <v>254</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="R11" s="30" t="s">
         <v>9</v>
@@ -3435,86 +3319,86 @@
         <v>44</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W11" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W11" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-11</v>
       </c>
       <c r="X11" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y11" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y11" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="57">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="56">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="58" t="s">
+      <c r="F12" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="G12" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M12" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N12" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Baliza</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Externa.Urbana</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>122</v>
+        <v>251</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="R12" s="30" t="s">
         <v>9</v>
@@ -3523,86 +3407,86 @@
         <v>44</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U12" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W12" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W12" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-12</v>
       </c>
       <c r="X12" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y12" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y12" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="57">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E13" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="58" t="s">
+      <c r="F13" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M13" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N13" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Difusa</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Feixe.Amplo</v>
       </c>
       <c r="P13" s="30" t="s">
         <v>123</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R13" s="30" t="s">
         <v>9</v>
@@ -3611,86 +3495,86 @@
         <v>44</v>
       </c>
       <c r="T13" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W13" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W13" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-13</v>
       </c>
       <c r="X13" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y13" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y13" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="57">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="58" t="s">
+      <c r="F14" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M14" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N14" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Embutida.Fixa</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Gôndola</v>
       </c>
       <c r="P14" s="30" t="s">
         <v>124</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="R14" s="30" t="s">
         <v>9</v>
@@ -3699,86 +3583,86 @@
         <v>44</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W14" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W14" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-14</v>
       </c>
       <c r="X14" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y14" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y14" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="57">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="63" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="58" t="s">
+      <c r="F15" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M15" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N15" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Embutida.Orientável</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Grande.Altura</v>
       </c>
       <c r="P15" s="30" t="s">
         <v>125</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="R15" s="30" t="s">
         <v>9</v>
@@ -3787,86 +3671,86 @@
         <v>44</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W15" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W15" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-15</v>
       </c>
       <c r="X15" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y15" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y15" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="57">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="56">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E16" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="58" t="s">
+      <c r="F16" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="34" t="str">
-        <f t="shared" ref="L16" si="13">CONCATENATE("", C16)</f>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M16" s="34" t="str">
-        <f t="shared" ref="M16" si="14">CONCATENATE("", D16)</f>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N16" s="34" t="str">
-        <f t="shared" ref="N16" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16" si="16">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
-        <v>Luz.Externa</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Hermética</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
@@ -3875,86 +3759,86 @@
         <v>44</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W16" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W16" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-16</v>
       </c>
       <c r="X16" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y16" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y16" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA16" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="56">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="57">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C17" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E17" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="63" t="s">
-        <v>260</v>
-      </c>
-      <c r="G17" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="58" t="s">
+      <c r="F17" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M17" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N17" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Externa.Urbana</v>
+        <f t="shared" si="8"/>
+        <v>Luz.LEDFita</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="R17" s="30" t="s">
         <v>9</v>
@@ -3963,86 +3847,86 @@
         <v>44</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U17" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W17" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W17" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-17</v>
       </c>
       <c r="X17" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y17" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y17" s="61" t="s">
+        <v>267</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="57">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="56">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E18" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="58" t="s">
+      <c r="F18" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M18" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N18" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Feixe.Amplo</v>
+        <f t="shared" si="8"/>
+        <v>Luz.LEDTubular</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="R18" s="30" t="s">
         <v>9</v>
@@ -4051,86 +3935,86 @@
         <v>44</v>
       </c>
       <c r="T18" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W18" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W18" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-18</v>
       </c>
       <c r="X18" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y18" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y18" s="61" t="s">
+        <v>267</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="57">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E19" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="63" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="58" t="s">
+      <c r="F19" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="G19" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L19" si="13">CONCATENATE("", C19)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M19" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="M19" si="14">CONCATENATE("", D19)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N19" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="N19" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
         <v>Luminária</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Gôndola</v>
+        <f t="shared" ref="O19" si="16">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),CONCATENATE("",F19))</f>
+        <v>Luz.TuboFluorescente</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="R19" s="30" t="s">
         <v>9</v>
@@ -4139,86 +4023,86 @@
         <v>44</v>
       </c>
       <c r="T19" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U19" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W19" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W19" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-19</v>
       </c>
       <c r="X19" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y19" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y19" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E20" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="58" t="s">
+      <c r="F20" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M20" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N20" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Grande.Altura</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Linear</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="R20" s="30" t="s">
         <v>9</v>
@@ -4227,86 +4111,86 @@
         <v>44</v>
       </c>
       <c r="T20" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U20" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W20" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W20" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-20</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y20" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y20" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="57">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E21" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="63" t="s">
+      <c r="F21" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="58" t="s">
+      <c r="G21" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M21" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N21" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Hermética</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Painel</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="R21" s="30" t="s">
         <v>9</v>
@@ -4315,83 +4199,83 @@
         <v>44</v>
       </c>
       <c r="T21" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U21" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W21" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W21" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-21</v>
       </c>
       <c r="X21" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y21" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y21" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="57">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="56">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E22" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="58" t="s">
+      <c r="F22" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M22" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N22" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.LEDFita</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Pendente</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q22" s="30" t="s">
         <v>142</v>
@@ -4403,86 +4287,86 @@
         <v>44</v>
       </c>
       <c r="T22" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U22" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W22" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W22" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-22</v>
       </c>
       <c r="X22" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y22" s="62" t="s">
-        <v>163</v>
+        <v>241</v>
+      </c>
+      <c r="Y22" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="57">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="56">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E23" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F23" s="63" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="58" t="s">
+      <c r="F23" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M23" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N23" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.LEDTubular</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Plafon</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R23" s="30" t="s">
         <v>9</v>
@@ -4491,86 +4375,86 @@
         <v>44</v>
       </c>
       <c r="T23" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U23" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W23" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W23" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-23</v>
       </c>
       <c r="X23" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y23" s="62" t="s">
-        <v>163</v>
+        <v>241</v>
+      </c>
+      <c r="Y23" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="57">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="56">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E24" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="63" t="s">
-        <v>254</v>
-      </c>
-      <c r="G24" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="58" t="s">
+      <c r="F24" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="G24" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="34" t="str">
-        <f t="shared" ref="L24" si="17">CONCATENATE("", C24)</f>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M24" s="34" t="str">
-        <f t="shared" ref="M24" si="18">CONCATENATE("", D24)</f>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N24" s="34" t="str">
-        <f t="shared" ref="N24" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" ref="O24" si="20">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
-        <v>Luz.TuboFluorescente</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Sensorizada</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="R24" s="30" t="s">
         <v>9</v>
@@ -4579,86 +4463,86 @@
         <v>44</v>
       </c>
       <c r="T24" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U24" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W24" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W24" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-24</v>
       </c>
       <c r="X24" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y24" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y24" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="57">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E25" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="63" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="58" t="s">
+      <c r="F25" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M25" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N25" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Linear</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Spot</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R25" s="30" t="s">
         <v>9</v>
@@ -4667,86 +4551,86 @@
         <v>44</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U25" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W25" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W25" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-25</v>
       </c>
       <c r="X25" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y25" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y25" s="61" t="s">
+        <v>268</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="57">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E26" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="58" t="s">
+      <c r="F26" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M26" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N26" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>Luminária</v>
       </c>
       <c r="O26" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Painel</v>
+        <f t="shared" si="8"/>
+        <v>Luz.Trilho</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R26" s="30" t="s">
         <v>9</v>
@@ -4755,86 +4639,86 @@
         <v>44</v>
       </c>
       <c r="T26" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U26" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W26" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W26" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-26</v>
       </c>
       <c r="X26" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y26" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y26" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="57">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>242</v>
+      </c>
+      <c r="G27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L27" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L27" si="17">CONCATENATE("", C27)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M27" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="M27" si="18">CONCATENATE("", D27)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N27" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Luminária</v>
+        <f t="shared" ref="N27" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
+        <v>Acessórios de Iluminação</v>
       </c>
       <c r="O27" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Pendente</v>
+        <f t="shared" ref="O27" si="20">IF(ISNUMBER(FIND("Ifc",F27)),CONCATENATE("Classe IFC:   ",F27),CONCATENATE("",F27))</f>
+        <v>Acessório.Luz</v>
       </c>
       <c r="P27" s="30" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="R27" s="30" t="s">
         <v>9</v>
@@ -4843,86 +4727,86 @@
         <v>44</v>
       </c>
       <c r="T27" s="30" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U27" s="30" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W27" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W27" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-27</v>
       </c>
       <c r="X27" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y27" s="62" t="s">
-        <v>162</v>
+        <v>241</v>
+      </c>
+      <c r="Y27" s="61" t="s">
+        <v>234</v>
       </c>
       <c r="Z27" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA27" s="30" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F28" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M28" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N28" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>Analítico de Luz</v>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Ponto.Iluminado</v>
+      </c>
+      <c r="P28" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="AA27" s="30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="57">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M28" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N28" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O28" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Plafon</v>
-      </c>
-      <c r="P28" s="30" t="s">
-        <v>135</v>
-      </c>
       <c r="Q28" s="30" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="R28" s="30" t="s">
         <v>9</v>
@@ -4931,86 +4815,86 @@
         <v>44</v>
       </c>
       <c r="T28" s="30" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="U28" s="30" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W28" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W28" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-28</v>
       </c>
       <c r="X28" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y28" s="62" t="s">
-        <v>162</v>
+        <v>9</v>
+      </c>
+      <c r="Y28" s="30" t="s">
+        <v>9</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>191</v>
+        <v>9</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="57">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="63" t="s">
-        <v>259</v>
-      </c>
-      <c r="G29" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="G29" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="57" t="s">
         <v>9</v>
       </c>
       <c r="L29" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M29" s="34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N29" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Luminária</v>
+        <f t="shared" si="2"/>
+        <v>Analítico de Luz</v>
       </c>
       <c r="O29" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Sensorizada</v>
+        <f t="shared" si="8"/>
+        <v>Linha.Iluminada</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="R29" s="30" t="s">
         <v>9</v>
@@ -5019,86 +4903,86 @@
         <v>44</v>
       </c>
       <c r="T29" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="U29" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="V29" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="W29" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-29</v>
+      </c>
+      <c r="X29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="30" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="56">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F30" s="62" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M30" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N30" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>Analítico de Luz</v>
+      </c>
+      <c r="O30" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Area.Iluminada</v>
+      </c>
+      <c r="P30" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="U29" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="V29" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W29" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-29</v>
-      </c>
-      <c r="X29" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y29" s="62" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z29" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA29" s="30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="57">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M30" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N30" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O30" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Spot</v>
-      </c>
-      <c r="P30" s="30" t="s">
-        <v>137</v>
-      </c>
       <c r="Q30" s="30" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="R30" s="30" t="s">
         <v>9</v>
@@ -5107,528 +4991,77 @@
         <v>44</v>
       </c>
       <c r="T30" s="30" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="U30" s="30" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W30" s="59" t="str">
-        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="W30" s="58" t="str">
+        <f t="shared" si="6"/>
         <v>Key-ILUM-30</v>
       </c>
       <c r="X30" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y30" s="62" t="s">
-        <v>252</v>
+        <v>9</v>
+      </c>
+      <c r="Y30" s="30" t="s">
+        <v>9</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>191</v>
+        <v>9</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="63" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L31" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M31" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N31" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O31" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Luz.Trilho</v>
-      </c>
-      <c r="P31" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q31" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="R31" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T31" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U31" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="V31" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W31" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-31</v>
-      </c>
-      <c r="X31" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y31" s="62" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z31" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA31" s="30" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="57">
-        <v>32</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E32" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="F32" s="63" t="s">
-        <v>253</v>
-      </c>
-      <c r="G32" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K32" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L32" s="34" t="str">
-        <f t="shared" ref="L32" si="21">CONCATENATE("", C32)</f>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M32" s="34" t="str">
-        <f t="shared" ref="M32" si="22">CONCATENATE("", D32)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N32" s="34" t="str">
-        <f t="shared" ref="N32" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
-        <v>Acessórios de Iluminação</v>
-      </c>
-      <c r="O32" s="30" t="str">
-        <f t="shared" ref="O32" si="24">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("Classe IFC:   ",F32),CONCATENATE("",F32))</f>
-        <v>Acessório.Luz</v>
-      </c>
-      <c r="P32" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q32" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="R32" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T32" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U32" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="V32" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W32" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-32</v>
-      </c>
-      <c r="X32" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y32" s="62" t="s">
-        <v>244</v>
-      </c>
-      <c r="Z32" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA32" s="30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="57">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E33" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="F33" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="G33" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L33" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M33" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N33" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Analítico de Luz</v>
-      </c>
-      <c r="O33" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Ponto.Iluminado</v>
-      </c>
-      <c r="P33" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q33" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="R33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T33" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="U33" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="V33" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W33" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-33</v>
-      </c>
-      <c r="X33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA33" s="30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="57">
-        <v>34</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="F34" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="G34" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L34" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M34" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N34" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Analítico de Luz</v>
-      </c>
-      <c r="O34" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Linha.Iluminada</v>
-      </c>
-      <c r="P34" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q34" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="R34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T34" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="U34" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="V34" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W34" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-34</v>
-      </c>
-      <c r="X34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA34" s="30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="57">
-        <v>35</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="F35" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="G35" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L35" s="34" t="str">
-        <f t="shared" si="5"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M35" s="34" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N35" s="34" t="str">
-        <f t="shared" si="7"/>
-        <v>Analítico de Luz</v>
-      </c>
-      <c r="O35" s="30" t="str">
-        <f t="shared" si="12"/>
-        <v>Area.Iluminada</v>
-      </c>
-      <c r="P35" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q35" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="R35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T35" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="U35" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="V35" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="W35" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-ILUM-35</v>
-      </c>
-      <c r="X35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA35" s="30" t="s">
-        <v>205</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA929">
-    <sortCondition ref="F7:F929"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA924">
+    <sortCondition ref="F2:F924"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B35">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B30">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA9:AA35">
-    <cfRule type="cellIs" dxfId="24" priority="49" operator="equal">
+  <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA4:AA30">
+    <cfRule type="cellIs" dxfId="19" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1485"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  <conditionalFormatting sqref="F2:F3">
+    <cfRule type="duplicateValues" dxfId="17" priority="1507"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F8">
-    <cfRule type="duplicateValues" dxfId="18" priority="1507"/>
+  <conditionalFormatting sqref="F4:F1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="1478"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1478"/>
+  <conditionalFormatting sqref="F26 F28:F30">
+    <cfRule type="duplicateValues" dxfId="15" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31 F33:F35">
-    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
+  <conditionalFormatting sqref="F31:F1048576 F4:F25">
+    <cfRule type="duplicateValues" dxfId="13" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1457"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F1048576 F9:F30">
-    <cfRule type="duplicateValues" dxfId="14" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1457"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X9:X32">
-    <cfRule type="containsText" dxfId="11" priority="43" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",X9)))</formula>
+  <conditionalFormatting sqref="X4:X27">
+    <cfRule type="containsText" dxfId="10" priority="43" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",X4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y30">
-    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
-    <cfRule type="containsText" dxfId="9" priority="41" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y30)))</formula>
+  <conditionalFormatting sqref="Y25">
+    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
+    <cfRule type="containsText" dxfId="8" priority="41" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y25)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="8" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="7" priority="42"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5638,15 +5071,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5711,7 +5144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5776,7 +5209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5859,30 +5292,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="80.3046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5941,15 +5374,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>85</v>
+        <v>179</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>265</v>
       </c>
       <c r="D2" s="51" t="s">
         <v>9</v>
@@ -5961,7 +5394,7 @@
         <v>79</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="H2" s="50" t="s">
         <v>9</v>
@@ -6000,33 +5433,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D3" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H3" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="J3" s="50" t="s">
         <v>9</v>
@@ -6041,51 +5474,51 @@
         <v>9</v>
       </c>
       <c r="N3" s="50" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="O3" s="25" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="P3" s="50" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="R3" s="50" t="s">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D4" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H4" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J4" s="50" t="s">
         <v>9</v>
@@ -6100,51 +5533,51 @@
         <v>9</v>
       </c>
       <c r="N4" s="50" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="P4" s="50" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="R4" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
+        <v>5</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="S4" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21">
-        <v>4</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>223</v>
-      </c>
       <c r="E5" s="35" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="H5" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J5" s="50" t="s">
         <v>9</v>
@@ -6159,51 +5592,51 @@
         <v>9</v>
       </c>
       <c r="N5" s="50" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="O5" s="25" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="P5" s="50" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="R5" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
+        <v>6</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="S5" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21">
-        <v>5</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>223</v>
-      </c>
       <c r="E6" s="35" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H6" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J6" s="50" t="s">
         <v>9</v>
@@ -6218,494 +5651,494 @@
         <v>9</v>
       </c>
       <c r="N6" s="50" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="P6" s="50" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="R6" s="50" t="s">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D7" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J7" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L7" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N7" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P7" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O7" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P7" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q7" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D8" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J8" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L8" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N8" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P8" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O8" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P8" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q8" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R8" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J9" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L9" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N9" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P9" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O9" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P9" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q9" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R9" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S9" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D10" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J10" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N10" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P10" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O10" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P10" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q10" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R10" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L11" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N11" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P11" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P11" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q11" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R11" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J12" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L12" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N12" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O12" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P12" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O12" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P12" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q12" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R12" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J13" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="L13" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="N13" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P13" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q13" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="R13" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="S13" s="25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21">
+        <v>14</v>
+      </c>
+      <c r="B14" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="K13" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L13" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="N13" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P13" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q13" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="R13" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="S13" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="21">
-        <v>13</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>236</v>
-      </c>
       <c r="C14" s="54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D14" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F14" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J14" s="50" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L14" s="50" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N14" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="O14" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="P14" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="O14" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="P14" s="50" t="s">
-        <v>212</v>
-      </c>
       <c r="Q14" s="25" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="R14" s="50" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="S14" s="25" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6718,15 +6151,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6749,7 +6182,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
